--- a/output/pdf_financials_xlsx/SBO.H.xlsx
+++ b/output/pdf_financials_xlsx/SBO.H.xlsx
@@ -6334,31 +6334,31 @@
         <v>0.019933</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.019933</v>
+        <v>0.013033</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.0069</v>
+        <v>0.01708</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.024497</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.01708</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -6366,19 +6366,19 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.021178</v>
       </c>
     </row>
     <row r="93">
@@ -9748,7 +9748,11 @@
           <t>Reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -11316,7 +11320,11 @@
           <t>Reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12488,7 +12496,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13486,7 +13498,11 @@
           <t>Reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14274,7 +14290,11 @@
           <t>Reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -14674,7 +14694,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -14975,7 +14999,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SBO.H.xlsx
+++ b/output/pdf_financials_xlsx/SBO.H.xlsx
@@ -1115,10 +1115,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000159</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2179,10 +2179,10 @@
         <v>-0.054118</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.074535</v>
+        <v>-0.074694</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.0602</v>
+        <v>-0.060202</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.144638</v>
@@ -2315,10 +2315,10 @@
         <v>-0.054118</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.074535</v>
+        <v>-0.074694</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.0602</v>
+        <v>-0.060202</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.144333</v>
@@ -2645,19 +2645,19 @@
         <v>0.082561</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.195835</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.075475</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004739</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000571</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00362</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
@@ -2674,19 +2674,19 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.4e-05</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.000102</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.006201</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.050831</v>
       </c>
     </row>
     <row r="35">
@@ -2765,19 +2765,19 @@
         <v>0.082561</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.195835</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.075475</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.004739</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000571</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00362</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0</v>
@@ -2794,19 +2794,19 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.4e-05</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.000102</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.006201</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.050831</v>
       </c>
     </row>
     <row r="37">
@@ -3485,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.195835</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.075475</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004401</v>
+        <v>0.000781</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.000505</v>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.012728</v>
+        <v>0.006527</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.053286</v>
+        <v>0.002455</v>
       </c>
     </row>
     <row r="49">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
